--- a/output/pdf_financials_xlsx/FC.xlsx
+++ b/output/pdf_financials_xlsx/FC.xlsx
@@ -2350,10 +2350,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1444339</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1444339</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1444339</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1444339</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -14725,7 +14725,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -16216,7 +16216,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -37015,7 +37015,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -38522,7 +38522,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -39147,7 +39147,7 @@
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
@@ -40112,7 +40112,7 @@
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -41328,7 +41328,7 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
@@ -42143,7 +42143,7 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E388" s="5" t="n">

--- a/output/pdf_financials_xlsx/FC.xlsx
+++ b/output/pdf_financials_xlsx/FC.xlsx
@@ -568,10 +568,8 @@
       <c r="E4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>0</v>
@@ -622,10 +620,8 @@
       <c r="E5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G5" s="3" t="n">
         <v>0</v>
@@ -680,10 +676,8 @@
       <c r="E6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>0</v>
@@ -734,10 +728,8 @@
       <c r="E7" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0</v>
@@ -788,10 +780,8 @@
       <c r="E8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G8" s="3" t="n">
         <v>0</v>
@@ -842,10 +832,8 @@
       <c r="E9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G9" s="3" t="n">
         <v>0</v>
@@ -896,10 +884,8 @@
       <c r="E10" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F10" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0</v>
@@ -954,10 +940,8 @@
       <c r="E11" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F11" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G11" s="3" t="n">
         <v>0</v>
@@ -1008,10 +992,8 @@
       <c r="E12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0</v>
@@ -1062,10 +1044,8 @@
       <c r="E13" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G13" s="3" t="n">
         <v>-0</v>
@@ -1116,10 +1096,8 @@
       <c r="E14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0</v>
@@ -1170,10 +1148,8 @@
       <c r="E15" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F15" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>0</v>
@@ -1224,10 +1200,8 @@
       <c r="E16" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F16" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>20081258</v>
@@ -1288,10 +1262,8 @@
       <c r="E17" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="F17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="G17" s="3" t="n">
         <v>-0</v>
@@ -1506,10 +1478,8 @@
       <c r="E20" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F20" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>20081258</v>
@@ -1570,10 +1540,8 @@
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0</v>
@@ -1624,10 +1592,8 @@
       <c r="E22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0</v>
@@ -1678,10 +1644,8 @@
       <c r="E23" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F23" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>20081258</v>
@@ -1956,10 +1920,8 @@
       <c r="E27" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F27" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>20081258</v>
@@ -2020,10 +1982,8 @@
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0</v>
@@ -2074,10 +2034,8 @@
       <c r="E29" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F29" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>20081258</v>
@@ -2214,10 +2172,8 @@
       <c r="E31" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F31" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0</v>
@@ -5854,10 +5810,8 @@
       <c r="E99" s="3" t="n">
         <v>16755292</v>
       </c>
-      <c r="F99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F99" s="3" t="n">
+        <v>19510113</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>20081258</v>
@@ -7869,7 +7823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S411"/>
+  <dimension ref="A1:S428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -39803,10 +39757,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I361" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I361" s="5" t="n">
+        <v>0.976</v>
       </c>
       <c r="J361" s="5" t="n">
         <v>0.991</v>
@@ -39888,10 +39840,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I362" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I362" s="5" t="n">
+        <v>0.965</v>
       </c>
       <c r="J362" s="5" t="n">
         <v>0.97</v>
@@ -40711,10 +40661,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B372" t="inlineStr"/>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Corporation manager interest allocation (note 13)</t>
+          <t>Bank indebtedness $ 41,713,128 $ 41,713,128 $</t>
         </is>
       </c>
       <c r="D372" t="inlineStr"/>
@@ -40728,11 +40682,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G372" s="5" t="n">
-        <v>1784991</v>
-      </c>
-      <c r="H372" s="5" t="n">
-        <v>2138032</v>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I372" t="inlineStr">
         <is>
@@ -40796,10 +40754,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B373" t="inlineStr"/>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Impairment loss on investment portfolio (note 5)</t>
+          <t>Accounts payable and accrued liabilities 2,195,415 2,195,415</t>
         </is>
       </c>
       <c r="D373" t="inlineStr"/>
@@ -40818,8 +40780,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H373" s="5" t="n">
-        <v>200000</v>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I373" t="inlineStr">
         <is>
@@ -40883,17 +40847,17 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B374" t="inlineStr"/>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Total comprehensive income and profit for the year $</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Loan on debenture portfolio investment 1,420,073 1,420,073</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr"/>
       <c r="E374" t="inlineStr">
         <is>
           <t>-</t>
@@ -40904,11 +40868,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G374" s="5" t="n">
-        <v>14659462</v>
-      </c>
-      <c r="H374" s="5" t="n">
-        <v>16755292</v>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I374" t="inlineStr">
         <is>
@@ -40974,12 +40942,12 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Profit per share</t>
+          <t>Total         year         1-3 years     4 - 6 years</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Shareholder dividend payable 2,701,754 2,701,754</t>
         </is>
       </c>
       <c r="D375" t="inlineStr"/>
@@ -40993,11 +40961,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G375" s="5" t="n">
-        <v>0.995</v>
-      </c>
-      <c r="H375" s="5" t="n">
-        <v>0.999</v>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I375" t="inlineStr">
         <is>
@@ -41063,12 +41035,12 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>Profit per share</t>
+          <t>Total         year         1-3 years     4 - 6 years</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Loans payable 7,093,535 7,093,535</t>
         </is>
       </c>
       <c r="D376" t="inlineStr"/>
@@ -41082,11 +41054,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G376" s="5" t="n">
-        <v>0.981</v>
-      </c>
-      <c r="H376" s="5" t="n">
-        <v>0.989</v>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I376" t="inlineStr">
         <is>
@@ -41150,10 +41126,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B377" t="inlineStr"/>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Interest and fees earned (note 15)</t>
+          <t>Convertible debentures 145,666,000 -</t>
         </is>
       </c>
       <c r="D377" t="inlineStr"/>
@@ -41162,26 +41142,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F377" s="5" t="n">
-        <v>20098195</v>
-      </c>
-      <c r="G377" s="5" t="n">
-        <v>22562666</v>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H377" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J377" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I377" s="5" t="n">
+        <v>114223000</v>
+      </c>
+      <c r="J377" s="5" t="n">
+        <v>31443000</v>
       </c>
       <c r="K377" t="inlineStr">
         <is>
@@ -41235,10 +41215,14 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B378" t="inlineStr"/>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Corporation manager interest allocation (note 15)</t>
+          <t>Subtotal - Liabilities 200,789,905 $ 55,123,905 $</t>
         </is>
       </c>
       <c r="D378" t="inlineStr"/>
@@ -41247,26 +41231,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F378" s="5" t="n">
-        <v>1394583</v>
-      </c>
-      <c r="G378" s="5" t="n">
-        <v>1784991</v>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J378" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I378" s="5" t="n">
+        <v>114223000</v>
+      </c>
+      <c r="J378" s="5" t="n">
+        <v>31443000</v>
       </c>
       <c r="K378" t="inlineStr">
         <is>
@@ -41320,27 +41304,31 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B379" t="inlineStr"/>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>Total         year         1-3 years     4 - 6 years</t>
+        </is>
+      </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Interest expense (note 16)</t>
-        </is>
-      </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
+          <t>Future advances under portfolio 113,464,052 113,464,052</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr"/>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F379" s="5" t="n">
-        <v>2877078</v>
-      </c>
-      <c r="G379" s="5" t="n">
-        <v>5348266</v>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H379" t="inlineStr">
         <is>
@@ -41411,12 +41399,12 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and</t>
+          <t>Total         year         1-3 years     4 - 6 years</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and distributions to unitholders</t>
+          <t>Liabilities and contractual obligations 314,376,957 $ 168,710,957 $</t>
         </is>
       </c>
       <c r="D380" t="inlineStr"/>
@@ -41425,26 +41413,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F380" s="5" t="n">
-        <v>14235843</v>
-      </c>
-      <c r="G380" s="5" t="n">
-        <v>14659462</v>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H380" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J380" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I380" s="5" t="n">
+        <v>114223000</v>
+      </c>
+      <c r="J380" s="5" t="n">
+        <v>31443000</v>
       </c>
       <c r="K380" t="inlineStr">
         <is>
@@ -41500,12 +41488,12 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and</t>
+          <t>SIGNIFICANT ACCOUNTING POLICIES</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Change in fair value of the conversion option of convertible debentures (note 4 (e)(ii))</t>
+          <t>A summary of significant accounting policies is described in note 3 of the Corporation’s financial statements for the year ended December 31, 2015 and year ended December</t>
         </is>
       </c>
       <c r="D381" t="inlineStr"/>
@@ -41514,8 +41502,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F381" s="5" t="n">
-        <v>-321826</v>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G381" t="inlineStr">
         <is>
@@ -41527,15 +41517,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J381" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I381" s="5" t="n">
+        <v>2014</v>
+      </c>
+      <c r="J381" s="5" t="n">
+        <v>31</v>
       </c>
       <c r="K381" t="inlineStr">
         <is>
@@ -41591,12 +41577,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Distribution to unitholders (note 10)</t>
+          <t>Interest and fees earned $</t>
         </is>
       </c>
       <c r="D382" t="inlineStr"/>
@@ -41605,8 +41591,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F382" s="5" t="n">
-        <v>-5731903</v>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G382" t="inlineStr">
         <is>
@@ -41618,15 +41606,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J382" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I382" s="5" t="n">
+        <v>30691450</v>
+      </c>
+      <c r="J382" s="5" t="n">
+        <v>34005435</v>
       </c>
       <c r="K382" t="inlineStr">
         <is>
@@ -41682,12 +41666,12 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>conversion option of convertible debentures and total</t>
+          <t>on our mortgage investments. total</t>
         </is>
       </c>
       <c r="D383" t="inlineStr"/>
@@ -41696,8 +41680,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F383" s="5" t="n">
-        <v>-6053729</v>
+      <c r="F383" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G383" t="inlineStr">
         <is>
@@ -41709,15 +41695,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J383" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I383" s="5" t="n">
+        <v>30691450</v>
+      </c>
+      <c r="J383" s="5" t="n">
+        <v>34005435</v>
       </c>
       <c r="K383" t="inlineStr">
         <is>
@@ -41773,12 +41755,12 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>year and change in net assets attributable</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>year and change in net assets attributable to unitholders for the year</t>
+          <t>Corporation manager interest allocation (note 13)</t>
         </is>
       </c>
       <c r="D384" t="inlineStr"/>
@@ -41787,26 +41769,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F384" s="5" t="n">
-        <v>8182114</v>
-      </c>
-      <c r="G384" s="5" t="n">
-        <v>14659462</v>
+      <c r="F384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H384" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J384" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I384" s="5" t="n">
+        <v>2586438</v>
+      </c>
+      <c r="J384" s="5" t="n">
+        <v>2873993</v>
       </c>
       <c r="K384" t="inlineStr">
         <is>
@@ -41862,15 +41844,19 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>Profit per Share</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Basic $</t>
-        </is>
-      </c>
-      <c r="D385" t="inlineStr"/>
+          <t>Interest expense (note 14)</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>
@@ -41881,23 +41867,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G385" s="5" t="n">
-        <v>0.995</v>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H385" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J385" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I385" s="5" t="n">
+        <v>7759154</v>
+      </c>
+      <c r="J385" s="5" t="n">
+        <v>9350610</v>
       </c>
       <c r="K385" t="inlineStr">
         <is>
@@ -41953,15 +41937,19 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>Profit per Share</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Diluted $</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr"/>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
@@ -41972,23 +41960,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G386" s="5" t="n">
-        <v>0.981</v>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H386" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="I386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J386" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I386" s="5" t="n">
+        <v>805745</v>
+      </c>
+      <c r="J386" s="5" t="n">
+        <v>829574</v>
       </c>
       <c r="K386" t="inlineStr">
         <is>
@@ -42044,20 +42030,24 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Interest and fees earned, net of Trust Manager</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Interest and fees earned, net of Trust Manager interest allocation (note 13)</t>
+          <t>Impairment loss on investment portfolio</t>
         </is>
       </c>
       <c r="D387" t="inlineStr"/>
-      <c r="E387" s="5" t="n">
-        <v>18401481</v>
-      </c>
-      <c r="F387" s="5" t="n">
-        <v>18703612</v>
+      <c r="E387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F387" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
@@ -42069,15 +42059,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J387" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I387" s="5" t="n">
+        <v>30000</v>
+      </c>
+      <c r="J387" s="5" t="n">
+        <v>870000</v>
       </c>
       <c r="K387" t="inlineStr">
         <is>
@@ -42133,24 +42119,28 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Interest and fees earned, net of Trust Manager</t>
+          <t>on our mortgage investments.</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Less interest expense (note 14)</t>
+          <t>Income and profit for the year $</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
-        </is>
-      </c>
-      <c r="E388" s="5" t="n">
-        <v>2820560</v>
-      </c>
-      <c r="F388" s="5" t="n">
-        <v>2877078</v>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F388" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G388" t="inlineStr">
         <is>
@@ -42162,15 +42152,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J388" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I388" s="5" t="n">
+        <v>19510113</v>
+      </c>
+      <c r="J388" s="5" t="n">
+        <v>20081258</v>
       </c>
       <c r="K388" t="inlineStr">
         <is>
@@ -42224,32 +42210,28 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B389" t="inlineStr">
-        <is>
-          <t>Interest and fees earned, net of Trust Manager</t>
-        </is>
-      </c>
+      <c r="B389" t="inlineStr"/>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Net interest and fee income</t>
+          <t>Corporation manager interest allocation (note 13)</t>
         </is>
       </c>
       <c r="D389" t="inlineStr"/>
-      <c r="E389" s="5" t="n">
-        <v>15580921</v>
-      </c>
-      <c r="F389" s="5" t="n">
-        <v>15826534</v>
-      </c>
-      <c r="G389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H389" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G389" s="5" t="n">
+        <v>1784991</v>
+      </c>
+      <c r="H389" s="5" t="n">
+        <v>2138032</v>
       </c>
       <c r="I389" t="inlineStr">
         <is>
@@ -42313,36 +42295,30 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B390" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B390" t="inlineStr"/>
       <c r="C390" t="inlineStr">
         <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E390" s="5" t="n">
-        <v>827725</v>
-      </c>
-      <c r="F390" s="5" t="n">
-        <v>1310691</v>
+          <t>Impairment loss on investment portfolio (note 5)</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G390" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H390" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H390" s="5" t="n">
+        <v>200000</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -42406,32 +42382,32 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B391" t="inlineStr">
-        <is>
-          <t>Expenses</t>
-        </is>
-      </c>
+      <c r="B391" t="inlineStr"/>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Change in unrealized loss in value of mortgages (note 5)</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr"/>
-      <c r="E391" s="5" t="n">
-        <v>300000</v>
-      </c>
-      <c r="F391" s="5" t="n">
-        <v>280000</v>
-      </c>
-      <c r="G391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H391" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Total comprehensive income and profit for the year $</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G391" s="5" t="n">
+        <v>14659462</v>
+      </c>
+      <c r="H391" s="5" t="n">
+        <v>16755292</v>
       </c>
       <c r="I391" t="inlineStr">
         <is>
@@ -42497,34 +42473,30 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Profit per share</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>Expenses total</t>
-        </is>
-      </c>
-      <c r="D392" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E392" s="5" t="n">
-        <v>1127725</v>
-      </c>
-      <c r="F392" s="5" t="n">
-        <v>1590691</v>
-      </c>
-      <c r="G392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H392" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Basic $</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G392" s="5" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="H392" s="5" t="n">
+        <v>0.999</v>
       </c>
       <c r="I392" t="inlineStr">
         <is>
@@ -42590,30 +42562,30 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Profit per share</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Net earnings for the year</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D393" t="inlineStr"/>
-      <c r="E393" s="5" t="n">
-        <v>14453196</v>
-      </c>
-      <c r="F393" s="5" t="n">
-        <v>14235843</v>
-      </c>
-      <c r="G393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H393" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G393" s="5" t="n">
+        <v>0.981</v>
+      </c>
+      <c r="H393" s="5" t="n">
+        <v>0.989</v>
       </c>
       <c r="I393" t="inlineStr">
         <is>
@@ -42677,27 +42649,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B394" t="inlineStr">
-        <is>
-          <t>Net earnings per unit</t>
-        </is>
-      </c>
+      <c r="B394" t="inlineStr"/>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Basic $</t>
+          <t>Interest and fees earned (note 15)</t>
         </is>
       </c>
       <c r="D394" t="inlineStr"/>
-      <c r="E394" s="5" t="n">
-        <v>1.041</v>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F394" s="5" t="n">
-        <v>1.008</v>
-      </c>
-      <c r="G394" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>20098195</v>
+      </c>
+      <c r="G394" s="5" t="n">
+        <v>22562666</v>
       </c>
       <c r="H394" t="inlineStr">
         <is>
@@ -42766,27 +42734,23 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B395" t="inlineStr">
-        <is>
-          <t>Net earnings per unit</t>
-        </is>
-      </c>
+      <c r="B395" t="inlineStr"/>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Diluted $</t>
+          <t>Corporation manager interest allocation (note 15)</t>
         </is>
       </c>
       <c r="D395" t="inlineStr"/>
-      <c r="E395" s="5" t="n">
-        <v>1.011</v>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F395" s="5" t="n">
-        <v>0.984</v>
-      </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1394583</v>
+      </c>
+      <c r="G395" s="5" t="n">
+        <v>1784991</v>
       </c>
       <c r="H395" t="inlineStr">
         <is>
@@ -42855,27 +42819,27 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B396" t="inlineStr">
-        <is>
-          <t>Trust units</t>
-        </is>
-      </c>
+      <c r="B396" t="inlineStr"/>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Balance, beginning of year</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr"/>
-      <c r="E396" s="5" t="n">
-        <v>131636584</v>
+          <t>Interest expense (note 16)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F396" s="5" t="n">
-        <v>132355149</v>
-      </c>
-      <c r="G396" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>2877078</v>
+      </c>
+      <c r="G396" s="5" t="n">
+        <v>5348266</v>
       </c>
       <c r="H396" t="inlineStr">
         <is>
@@ -42946,25 +42910,25 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Trust units</t>
+          <t>conversion option of convertible debentures and</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of units</t>
+          <t>conversion option of convertible debentures and distributions to unitholders</t>
         </is>
       </c>
       <c r="D397" t="inlineStr"/>
-      <c r="E397" s="5" t="n">
-        <v>204583</v>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F397" s="5" t="n">
-        <v>4818103</v>
-      </c>
-      <c r="G397" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>14235843</v>
+      </c>
+      <c r="G397" s="5" t="n">
+        <v>14659462</v>
       </c>
       <c r="H397" t="inlineStr">
         <is>
@@ -43035,20 +42999,22 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Trust units</t>
+          <t>conversion option of convertible debentures and</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Conversion of debentures to units 20,000</t>
+          <t>Change in fair value of the conversion option of convertible debentures (note 4 (e)(ii))</t>
         </is>
       </c>
       <c r="D398" t="inlineStr"/>
-      <c r="E398" s="5" t="n">
-        <v>982</v>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F398" s="5" t="n">
-        <v>513</v>
+        <v>-321826</v>
       </c>
       <c r="G398" t="inlineStr">
         <is>
@@ -43124,20 +43090,22 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>Trust units</t>
+          <t>conversion option of convertible debentures and</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Balance, end of year</t>
+          <t>Distribution to unitholders (note 10)</t>
         </is>
       </c>
       <c r="D399" t="inlineStr"/>
-      <c r="E399" s="5" t="n">
-        <v>132355149</v>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F399" s="5" t="n">
-        <v>137193252</v>
+        <v>-5731903</v>
       </c>
       <c r="G399" t="inlineStr">
         <is>
@@ -43213,20 +43181,22 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Equity component of convertible debenture</t>
+          <t>conversion option of convertible debentures and</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Balance, beginning of year</t>
+          <t>conversion option of convertible debentures and total</t>
         </is>
       </c>
       <c r="D400" t="inlineStr"/>
-      <c r="E400" s="5" t="n">
-        <v>380482</v>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F400" s="5" t="n">
-        <v>372324</v>
+        <v>-6053729</v>
       </c>
       <c r="G400" t="inlineStr">
         <is>
@@ -43302,12 +43272,12 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>Equity component of convertible debenture</t>
+          <t>year and change in net assets attributable</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Equity component of debenture issued during the year</t>
+          <t>year and change in net assets attributable to unitholders for the year</t>
         </is>
       </c>
       <c r="D401" t="inlineStr"/>
@@ -43317,12 +43287,10 @@
         </is>
       </c>
       <c r="F401" s="5" t="n">
-        <v>230000</v>
-      </c>
-      <c r="G401" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>8182114</v>
+      </c>
+      <c r="G401" s="5" t="n">
+        <v>14659462</v>
       </c>
       <c r="H401" t="inlineStr">
         <is>
@@ -43393,27 +43361,27 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Equity component of convertible debenture</t>
+          <t>Profit per Share</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Conversion of debentures to units</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D402" t="inlineStr"/>
-      <c r="E402" s="5" t="n">
-        <v>-8158</v>
+      <c r="E402" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G402" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G402" s="5" t="n">
+        <v>0.995</v>
       </c>
       <c r="H402" t="inlineStr">
         <is>
@@ -43484,25 +43452,27 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>Equity component of convertible debenture</t>
+          <t>Profit per Share</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Balance, end of year</t>
+          <t>Diluted $</t>
         </is>
       </c>
       <c r="D403" t="inlineStr"/>
-      <c r="E403" s="5" t="n">
-        <v>372324</v>
-      </c>
-      <c r="F403" s="5" t="n">
-        <v>602324</v>
-      </c>
-      <c r="G403" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F403" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G403" s="5" t="n">
+        <v>0.981</v>
       </c>
       <c r="H403" t="inlineStr">
         <is>
@@ -43573,20 +43543,20 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>Cumulative earnings</t>
+          <t>Interest and fees earned, net of Trust Manager</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Balance, beginning of year</t>
+          <t>Interest and fees earned, net of Trust Manager interest allocation (note 13)</t>
         </is>
       </c>
       <c r="D404" t="inlineStr"/>
       <c r="E404" s="5" t="n">
-        <v>80874768</v>
+        <v>18401481</v>
       </c>
       <c r="F404" s="5" t="n">
-        <v>95327964</v>
+        <v>18703612</v>
       </c>
       <c r="G404" t="inlineStr">
         <is>
@@ -43662,20 +43632,24 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Cumulative earnings</t>
+          <t>Interest and fees earned, net of Trust Manager</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Net earnings for the year</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr"/>
+          <t>Less interest expense (note 14)</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E405" s="5" t="n">
-        <v>14453196</v>
+        <v>2820560</v>
       </c>
       <c r="F405" s="5" t="n">
-        <v>14235843</v>
+        <v>2877078</v>
       </c>
       <c r="G405" t="inlineStr">
         <is>
@@ -43751,20 +43725,20 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Cumulative earnings</t>
+          <t>Interest and fees earned, net of Trust Manager</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Balance, end of year $</t>
+          <t>Net interest and fee income</t>
         </is>
       </c>
       <c r="D406" t="inlineStr"/>
       <c r="E406" s="5" t="n">
-        <v>95327964</v>
+        <v>15580921</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>109563807</v>
+        <v>15826534</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>
@@ -43840,20 +43814,24 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Cumulative distributions to unitholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Balance, beginning of year</t>
-        </is>
-      </c>
-      <c r="D407" t="inlineStr"/>
+          <t>General and administrative</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E407" s="5" t="n">
-        <v>80874768</v>
+        <v>827725</v>
       </c>
       <c r="F407" s="5" t="n">
-        <v>95327964</v>
+        <v>1310691</v>
       </c>
       <c r="G407" t="inlineStr">
         <is>
@@ -43929,20 +43907,20 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>Cumulative distributions to unitholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Distributions to unitholders (note 11)</t>
+          <t>Change in unrealized loss in value of mortgages (note 5)</t>
         </is>
       </c>
       <c r="D408" t="inlineStr"/>
       <c r="E408" s="5" t="n">
-        <v>14453196</v>
+        <v>300000</v>
       </c>
       <c r="F408" s="5" t="n">
-        <v>14235843</v>
+        <v>280000</v>
       </c>
       <c r="G408" t="inlineStr">
         <is>
@@ -44018,20 +43996,24 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>Cumulative distributions to unitholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Balance, end of year</t>
-        </is>
-      </c>
-      <c r="D409" t="inlineStr"/>
+          <t>Expenses total</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E409" s="5" t="n">
-        <v>95327964</v>
+        <v>1127725</v>
       </c>
       <c r="F409" s="5" t="n">
-        <v>109563807</v>
+        <v>1590691</v>
       </c>
       <c r="G409" t="inlineStr">
         <is>
@@ -44107,20 +44089,20 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>Cumulative distributions to unitholders</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Total unitholders’ equity</t>
+          <t>Net earnings for the year</t>
         </is>
       </c>
       <c r="D410" t="inlineStr"/>
       <c r="E410" s="5" t="n">
-        <v>132727473</v>
+        <v>14453196</v>
       </c>
       <c r="F410" s="5" t="n">
-        <v>137795676</v>
+        <v>14235843</v>
       </c>
       <c r="G410" t="inlineStr">
         <is>
@@ -44196,82 +44178,1599 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>Cumulative distributions to unitholders</t>
+          <t>Net earnings per unit</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Units issued and outstanding (note 9)</t>
+          <t>Basic $</t>
         </is>
       </c>
       <c r="D411" t="inlineStr"/>
       <c r="E411" s="5" t="n">
+        <v>1.041</v>
+      </c>
+      <c r="F411" s="5" t="n">
+        <v>1.008</v>
+      </c>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Net earnings per unit</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Diluted $</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" s="5" t="n">
+        <v>1.011</v>
+      </c>
+      <c r="F412" s="5" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Trust units</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" s="5" t="n">
+        <v>131636584</v>
+      </c>
+      <c r="F413" s="5" t="n">
+        <v>132355149</v>
+      </c>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Trust units</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Proceeds from issuance of units</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" s="5" t="n">
+        <v>204583</v>
+      </c>
+      <c r="F414" s="5" t="n">
+        <v>4818103</v>
+      </c>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S414" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Trust units</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Conversion of debentures to units 20,000</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" s="5" t="n">
+        <v>982</v>
+      </c>
+      <c r="F415" s="5" t="n">
+        <v>513</v>
+      </c>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Trust units</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Balance, end of year</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" s="5" t="n">
+        <v>132355149</v>
+      </c>
+      <c r="F416" s="5" t="n">
+        <v>137193252</v>
+      </c>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Equity component of convertible debenture</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" s="5" t="n">
+        <v>380482</v>
+      </c>
+      <c r="F417" s="5" t="n">
+        <v>372324</v>
+      </c>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S417" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Equity component of convertible debenture</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Equity component of debenture issued during the year</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F418" s="5" t="n">
+        <v>230000</v>
+      </c>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Equity component of convertible debenture</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Conversion of debentures to units</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" s="5" t="n">
+        <v>-8158</v>
+      </c>
+      <c r="F419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S419" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>Equity component of convertible debenture</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Balance, end of year</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" s="5" t="n">
+        <v>372324</v>
+      </c>
+      <c r="F420" s="5" t="n">
+        <v>602324</v>
+      </c>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S420" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>Cumulative earnings</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" s="5" t="n">
+        <v>80874768</v>
+      </c>
+      <c r="F421" s="5" t="n">
+        <v>95327964</v>
+      </c>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S421" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>Cumulative earnings</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Net earnings for the year</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" s="5" t="n">
+        <v>14453196</v>
+      </c>
+      <c r="F422" s="5" t="n">
+        <v>14235843</v>
+      </c>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S422" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>Cumulative earnings</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Balance, end of year $</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" s="5" t="n">
+        <v>95327964</v>
+      </c>
+      <c r="F423" s="5" t="n">
+        <v>109563807</v>
+      </c>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S423" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>Cumulative distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Balance, beginning of year</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" s="5" t="n">
+        <v>80874768</v>
+      </c>
+      <c r="F424" s="5" t="n">
+        <v>95327964</v>
+      </c>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S424" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Cumulative distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Distributions to unitholders (note 11)</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" s="5" t="n">
+        <v>14453196</v>
+      </c>
+      <c r="F425" s="5" t="n">
+        <v>14235843</v>
+      </c>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Cumulative distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Balance, end of year</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" s="5" t="n">
+        <v>95327964</v>
+      </c>
+      <c r="F426" s="5" t="n">
+        <v>109563807</v>
+      </c>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S426" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Cumulative distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Total unitholders’ equity</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" s="5" t="n">
+        <v>132727473</v>
+      </c>
+      <c r="F427" s="5" t="n">
+        <v>137795676</v>
+      </c>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S427" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Cumulative distributions to unitholders</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Units issued and outstanding (note 9)</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" s="5" t="n">
         <v>13896829</v>
       </c>
-      <c r="F411" s="5" t="n">
+      <c r="F428" s="5" t="n">
         <v>14377333</v>
       </c>
-      <c r="G411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R411" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S411" t="inlineStr">
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R428" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S428" t="inlineStr">
         <is>
           <t>-</t>
         </is>
